--- a/event_planner_forms/006_vote_exam_date_flat_color--event_planner_forms.xlsx
+++ b/event_planner_forms/006_vote_exam_date_flat_color--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'red'}</t>
+          <t>red</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Red'}</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'blue'}</t>
+          <t>blue</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Blue'}</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'green'}</t>
+          <t>green</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Green'}</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'flat'}</t>
+          <t>flat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Flat'}</t>
+          <t>Flat</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'colorful'}</t>
+          <t>colorful</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Colorful'}</t>
+          <t>Colorful</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'center'}</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Center'}</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'top_left'}</t>
+          <t>top_left</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Top Left'}</t>
+          <t>Top Left</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'bottom_right'}</t>
+          <t>bottom_right</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Bottom Right'}</t>
+          <t>Bottom Right</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'10%'}</t>
+          <t>10%</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '10%'}</t>
+          <t>10%</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'50%'}</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '50%'}</t>
+          <t>50%</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'100%'}</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '100%'}</t>
+          <t>100%</t>
         </is>
       </c>
     </row>
